--- a/用卷/xlsx/常规科目/1987.xlsx
+++ b/用卷/xlsx/常规科目/1987.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A935AFFE-0AB1-411A-8436-6A133A8CC620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208723FD-5F64-40DA-A0C2-7D468C3D8EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
   <si>
     <t>年份</t>
   </si>
@@ -48,9 +48,6 @@
     <t>山西</t>
   </si>
   <si>
-    <t>辽宁</t>
-  </si>
-  <si>
     <t>吉林</t>
   </si>
   <si>
@@ -66,18 +63,12 @@
     <t>山东</t>
   </si>
   <si>
-    <t>湖北</t>
-  </si>
-  <si>
     <t>湖南</t>
   </si>
   <si>
     <t>广东</t>
   </si>
   <si>
-    <t>广西</t>
-  </si>
-  <si>
     <t>四川</t>
   </si>
   <si>
@@ -88,9 +79,6 @@
   </si>
   <si>
     <t>西藏</t>
-  </si>
-  <si>
-    <t>陕西</t>
   </si>
   <si>
     <t>青海</t>
@@ -374,6 +362,34 @@
       </rPr>
       <t>,上海卷</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西英语类</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西其他类</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>辽宁文史类</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>陕西英语类</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>陕西其他类</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北文史类</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北其他类</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -828,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -838,7 +854,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -859,10 +875,10 @@
         <v>1987</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -873,7 +889,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -881,10 +897,10 @@
         <v>1987</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -892,10 +908,10 @@
         <v>1987</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -903,10 +919,10 @@
         <v>1987</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -914,10 +930,10 @@
         <v>1987</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -928,7 +944,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -939,7 +955,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -947,21 +963,21 @@
         <v>1987</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="8">
+        <v>1987</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>1987</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -969,10 +985,10 @@
         <v>1987</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -980,10 +996,10 @@
         <v>1987</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -991,10 +1007,10 @@
         <v>1987</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1002,10 +1018,10 @@
         <v>1987</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1013,10 +1029,10 @@
         <v>1987</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1024,10 +1040,10 @@
         <v>1987</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1035,10 +1051,10 @@
         <v>1987</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1046,10 +1062,10 @@
         <v>1987</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1057,10 +1073,10 @@
         <v>1987</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1068,54 +1084,54 @@
         <v>1987</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>1987</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>12</v>
+      <c r="A23" s="8">
+        <v>1987</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>1987</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>13</v>
+      <c r="B24" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="10">
-        <v>1987</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>62</v>
+      <c r="A25" s="1">
+        <v>1987</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>1987</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>14</v>
+      <c r="A26" s="10">
+        <v>1987</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1123,32 +1139,32 @@
         <v>1987</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>1987</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>16</v>
+      <c r="A28" s="8">
+        <v>1987</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="10">
-        <v>1988</v>
+      <c r="A29" s="1">
+        <v>1987</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1156,21 +1172,21 @@
         <v>1987</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
-        <v>1987</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
+      <c r="A31" s="10">
+        <v>1988</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1178,10 +1194,10 @@
         <v>1987</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1189,180 +1205,213 @@
         <v>1987</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>1987</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>40</v>
+      <c r="B34" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
-        <v>1987</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>21</v>
+      <c r="A35" s="8">
+        <v>1987</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>1987</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>22</v>
+      <c r="B36" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="7">
-        <v>1987</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>23</v>
+      <c r="A37" s="1">
+        <v>1987</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="2"/>
+      <c r="A38" s="1">
+        <v>1987</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
+      <c r="A39" s="1">
+        <v>1987</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>26</v>
+      <c r="A40" s="7">
+        <v>1987</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="4">
-        <v>3</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>65</v>
-      </c>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" s="4">
-        <v>5</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>66</v>
-      </c>
+      <c r="A42" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" s="4">
-        <v>3</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>67</v>
+        <v>20</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B44" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B45" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="17">
-        <v>1</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="B46" s="4">
+        <v>3</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="18"/>
-      <c r="C47" s="16"/>
+        <v>26</v>
+      </c>
+      <c r="B47" s="4">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="10">
-        <v>7</v>
+      <c r="A48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" s="4">
+        <v>2</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" s="4">
+        <v>28</v>
+      </c>
+      <c r="B49" s="17">
         <v>1</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>48</v>
+      <c r="C49" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" s="18"/>
+      <c r="C50" s="16"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="10">
+        <v>7</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="4">
+        <v>1</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B49:B50"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
